--- a/output/risk_register.xlsx
+++ b/output/risk_register.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="Risk Register" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="CSF Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Control Priorities" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="CSF Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -58,11 +59,6 @@
         <fgColor rgb="00FFD966"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0092D050"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -76,24 +72,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -471,137 +462,137 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="45" customWidth="1" min="10" max="10"/>
-    <col width="45" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
     <col width="17" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="17" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
-    <col width="17" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="19" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="45" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Risk ID</t>
+          <t>risk_id</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Risk</t>
+          <t>risk</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Threat Scenario</t>
+          <t>scenario</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>CSF Function</t>
+          <t>csf_function</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>CSF Category</t>
+          <t>csf_category</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CSF Subcategory</t>
+          <t>csf_subcategory</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>asset</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Likelihood</t>
+          <t>inherent_likelihood</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Impact</t>
+          <t>inherent_impact</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Existing Controls</t>
+          <t>inherent_score</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Recommended Treatment</t>
+          <t>inherent_rating</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Residual Likelihood</t>
+          <t>residual_likelihood</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Residual Impact</t>
+          <t>residual_impact</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>residual_score</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Timeline</t>
+          <t>residual_rating</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Inherent Score</t>
+          <t>risk_reduction_pct</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Inherent Rating</t>
+          <t>open_control_gaps</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Residual Score</t>
+          <t>owner</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Residual Rating</t>
+          <t>timeline</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Risk Reduction %</t>
+          <t>treatment</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>R01</t>
+          <t>R06</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Phishing-led initial access</t>
+          <t>Excessive privileges / domain admin compromise</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Employee opens malicious attachment/link that drops a loader and ransomware</t>
+          <t>Attacker escalates to domain admin and deploys ransomware domain-wide</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -611,85 +602,85 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>PR.AT</t>
+          <t>PR.AA</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>PR.AT-01</t>
+          <t>PR.AA-05</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Workforce / email</t>
+          <t>Active Directory</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I2" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="I2" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Annual awareness training; basic spam filter</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>Monthly phishing simulations; email sandboxing; report-phish button</t>
+      <c r="J2" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>CISO</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>0-90 days</t>
+        <v>5</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
       <c r="P2" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="S2" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="T2" s="2" t="n">
-        <v>55</v>
+        <v>0</v>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>C08, C13</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>IT Infrastructure</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>30-120 days</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>Privileged Access Management; tiered admin model; LAPS; remove standing admin rights</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>R02</t>
+          <t>R08</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Remote access without MFA</t>
+          <t>Backups not immutable or offline</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Attacker uses stolen credentials on VPN/RDP exposed to the internet</t>
+          <t>Attacker deletes or encrypts backups before detonation</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -699,17 +690,17 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>PR.AA</t>
+          <t>PR.DS</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>PR.AA-03</t>
+          <t>PR.DS-11</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>VPN / RDP gateways</t>
+          <t>Backup infrastructure</t>
         </is>
       </c>
       <c r="H3" s="2" t="n">
@@ -718,50 +709,50 @@
       <c r="I3" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>Password-only VPN</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>Phishing-resistant MFA; close public RDP; geo/IP restrictions</t>
+      <c r="J3" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>IT Infrastructure</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>0-30 days</t>
+        <v>5</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
       <c r="P3" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q3" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="S3" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="T3" s="2" t="n">
-        <v>60</v>
+        <v>0</v>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>IT Operations</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>0-60 days</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>3-2-1-1-0 strategy; immutable/air-gapped copy; separate backup credentials with MFA</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -801,71 +792,71 @@
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Monthly patch cycle</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>C05, C07</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>IT Operations</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0-60 days</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>72-hour SLA for actively exploited CVEs (CISA KEV); attack-surface scanning</t>
         </is>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>IT Operations</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0-60 days</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="S4" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="n">
-        <v>60</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>R06</t>
+          <t>R02</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Excessive privileges / domain admin compromise</t>
+          <t>Remote access without MFA</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Attacker escalates to domain admin and deploys ransomware domain-wide</t>
+          <t>Attacker uses stolen credentials on VPN/RDP exposed to the internet</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -880,12 +871,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>PR.AA-05</t>
+          <t>PR.AA-03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Active Directory</t>
+          <t>VPN / RDP gateways</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
@@ -894,66 +885,66 @@
       <c r="I5" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>Shared admin accounts</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>Privileged Access Management; tiered admin model; LAPS; remove standing admin rights</t>
+      <c r="J5" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>C03, C04</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>IT Infrastructure</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>30-120 days</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="S5" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="n">
-        <v>60</v>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>0-30 days</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>Phishing-resistant MFA; close public RDP; geo/IP restrictions</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>R07</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Flat network enabling lateral movement</t>
+          <t>Data exfiltration (double extortion)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Ransomware spreads rapidly across servers and workstations</t>
+          <t>Data stolen before encryption and leaked to force payment</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -963,17 +954,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>PR.IR</t>
+          <t>PR.DS</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>PR.IR-01</t>
+          <t>PR.DS-01</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Corporate network</t>
+          <t>Sensitive data stores</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
@@ -982,226 +973,226 @@
       <c r="I6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>Partial VLANs</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>Segment crown jewels; restrict SMB/RDP east-west; micro-segmentation</t>
+      <c r="J6" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>Network Team</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+        <v>4.5</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>C13, C14, C15</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>CISO / DPO</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>60-180 days</t>
         </is>
       </c>
-      <c r="P6" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q6" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="S6" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="n">
-        <v>60</v>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>Data classification; DLP; egress filtering; encryption at rest</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>R08</t>
+          <t>R11</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Backups not immutable or offline</t>
+          <t>Insufficient logging and no 24/7 monitoring</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Attacker deletes or encrypts backups before detonation</t>
+          <t>Intrusion goes unnoticed for days before encryption</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Protect</t>
+          <t>Detect</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>PR.DS</t>
+          <t>DE.AE</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>PR.DS-11</t>
+          <t>DE.AE-02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Backup infrastructure</t>
+          <t>SIEM / logs</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
         <v>4</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>Nightly backups on domain-joined storage</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3-2-1-1-0 strategy; immutable/air-gapped copy; separate backup credentials with MFA</t>
+        <v>4</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>IT Operations</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0-60 days</t>
+        <v>4</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="P7" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q7" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="S7" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="n">
-        <v>70</v>
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>Security Team</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>60-180 days</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>Central SIEM; MDR/SOC 24/7; alerts for mass file changes and backup tampering</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R18</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Data exfiltration (double extortion)</t>
+          <t>No Business Impact Analysis (RTO/RPO unknown)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Data stolen before encryption and leaked to force payment</t>
+          <t>Recovery not prioritised by business criticality</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Protect</t>
+          <t>Identify</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>PR.DS</t>
+          <t>ID.AM</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>PR.DS-01</t>
+          <t>ID.AM-05</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Sensitive data stores</t>
+          <t>Critical services</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
         <v>4</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>No DLP; limited encryption</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>Data classification; DLP; egress filtering; encryption at rest</t>
+        <v>4</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>CISO / DPO</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>60-180 days</t>
+      <c r="N8" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="P8" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q8" s="3" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="S8" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="n">
-        <v>40</v>
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>C21</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>Business Continuity</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>60-120 days</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>Complete BIA; define RTO/RPO; rank systems for restoration</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1246,86 +1237,86 @@
       <c r="I9" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>No scheduled restore tests</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>C11, C22</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>IT Operations</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>30-90 days</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
         <is>
           <t>Quarterly restore tests; verify integrity and malware-free before restore</t>
         </is>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>IT Operations</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>30-90 days</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q9" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="S9" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="n">
-        <v>62</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>R21</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>No EDR on endpoints and servers</t>
+          <t>Credential theft via infostealers</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Ransomware executes undetected on unmanaged or legacy-AV hosts</t>
+          <t>Stolen browser-saved credentials sold and used for access</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Detect</t>
+          <t>Protect</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>DE.CM</t>
+          <t>PR.AA</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>DE.CM-09</t>
+          <t>PR.AA-01</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Endpoints / servers</t>
+          <t>User credentials</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
@@ -1334,262 +1325,262 @@
       <c r="I10" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>Signature-based antivirus</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>Deploy EDR with ransomware behaviour rules and auto-isolation</t>
+      <c r="J10" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>C01, C03, C24</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>Security Team</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>30-90 days</t>
         </is>
       </c>
-      <c r="P10" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q10" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="S10" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>62</v>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>Password manager; MFA everywhere; dark-web credential monitoring</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>R11</t>
+          <t>R15</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Insufficient logging and no 24/7 monitoring</t>
+          <t>Third-party / supply chain compromise</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Intrusion goes unnoticed for days before encryption</t>
+          <t>Vendor or MSP compromised and used to push ransomware</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Detect</t>
+          <t>Govern</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>DE.AE</t>
+          <t>GV.SC</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>DE.AE-02</t>
+          <t>GV.SC-07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>SIEM / logs</t>
+          <t>Vendors / MSPs</t>
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>Local logs, no central SIEM</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>Central SIEM; MDR/SOC 24/7; alerts for mass file changes and backup tampering</t>
+        <v>5</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>Security Team</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>60-180 days</t>
+        <v>5</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="P11" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q11" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="S11" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="n">
-        <v>62</v>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>C18</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>Procurement / CISO</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>90-180 days</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>Vendor risk assessments; security clauses; least-privilege vendor access</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>R18</t>
+          <t>R22</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>No Business Impact Analysis (RTO/RPO unknown)</t>
+          <t>Unmanaged legacy / OT systems</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Recovery not prioritised by business criticality</t>
+          <t>Unpatchable systems are easy targets and halt operations when encrypted</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Identify</t>
+          <t>Protect</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>ID.AM</t>
+          <t>PR.PS</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>ID.AM-05</t>
+          <t>PR.PS-01</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Critical services</t>
+          <t>Legacy / OT</t>
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>Complete BIA; define RTO/RPO; rank systems for restoration</t>
+        <v>5</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
         <v>3</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>Business Continuity</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>60-120 days</t>
+        <v>5</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="P12" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q12" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="S12" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="n">
-        <v>44</v>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>C25</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>IT / Operations</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>90-240 days</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>Isolate legacy systems; virtual patching; compensating controls</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>R21</t>
+          <t>R05</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Credential theft via infostealers</t>
+          <t>Weak vulnerability management</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Stolen browser-saved credentials sold and used for access</t>
+          <t>Scans run irregularly; findings not prioritised by exploitability</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Protect</t>
+          <t>Identify</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>PR.AA</t>
+          <t>ID.RA</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>PR.AA-01</t>
+          <t>ID.RA-01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>User credentials</t>
+          <t>Servers / endpoints</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
@@ -1598,66 +1589,66 @@
       <c r="I13" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>Complexity policy only</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>Password manager; MFA everywhere; dark-web credential monitoring</t>
+      <c r="J13" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>C05, C06, C07</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>Security Team</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>30-90 days</t>
         </is>
       </c>
-      <c r="P13" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q13" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="S13" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="n">
-        <v>44</v>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>Continuous scanning; risk-based prioritisation; remediation tracking KPIs</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>R13</t>
+          <t>R14</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>No tested incident response plan</t>
+          <t>Poor crisis communication and legal notification</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Slow, uncoordinated response increases dwell time and damage</t>
+          <t>Delayed regulator/customer/staff notification causes fines and reputational loss</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1667,773 +1658,773 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>RS.MA</t>
+          <t>RS.CO</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>RS.MA-01</t>
+          <t>RS.CO-02</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>IR capability</t>
+          <t>Legal / Comms</t>
         </is>
       </c>
       <c r="H14" s="2" t="n">
         <v>3</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>Draft IR plan, never exercised</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>Ransomware playbook; biannual tabletop exercises; IR retainer</t>
+        <v>4</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>CISO</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>C17</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>Legal / Comms</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>30-90 days</t>
         </is>
       </c>
-      <c r="P14" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q14" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="S14" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="n">
-        <v>60</v>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>Comms plan; legal counsel on call; regulatory notification matrix</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>R15</t>
+          <t>R01</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Third-party / supply chain compromise</t>
+          <t>Phishing-led initial access</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Vendor or MSP compromised and used to push ransomware</t>
+          <t>Employee opens malicious attachment/link that drops a loader and ransomware</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Govern</t>
+          <t>Protect</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>GV.SC</t>
+          <t>PR.AT</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>GV.SC-07</t>
+          <t>PR.AT-01</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Vendors / MSPs</t>
+          <t>Workforce / email</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>Contracts lack security clauses</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>Vendor risk assessments; security clauses; least-privilege vendor access</t>
+        <v>4</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>2</v>
+        <v>2.91</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>Procurement / CISO</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>90-180 days</t>
+      <c r="N15" s="2" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="P15" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q15" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="S15" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="n">
-        <v>47</v>
+        <v>42</v>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>C01, C12</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>CISO</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>0-90 days</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>Monthly phishing simulations; email sandboxing; report-phish button</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>R19</t>
+          <t>R07</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Outdated disaster recovery plan</t>
+          <t>Flat network enabling lateral movement</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Recovery of critical systems takes weeks</t>
+          <t>Ransomware spreads rapidly across servers and workstations</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Recover</t>
+          <t>Protect</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>RC.RP</t>
+          <t>PR.IR</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>RC.RP-01</t>
+          <t>PR.IR-01</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>DR plan</t>
+          <t>Corporate network</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I16" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>DR plan outdated</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>Update DR plan; restoration runbooks; clean-room recovery environment</t>
+      <c r="J16" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>2</v>
+        <v>2.79</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>IT Operations</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>60-150 days</t>
+        <v>4.12</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="P16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q16" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="S16" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="n">
-        <v>60</v>
+        <v>42</v>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>C08, C09, C12</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>Network Team</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>60-180 days</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>Segment crown jewels; restrict SMB/RDP east-west; micro-segmentation</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>R22</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Unmanaged legacy / OT systems</t>
+          <t>No EDR on endpoints and servers</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Unpatchable systems are easy targets and halt operations when encrypted</t>
+          <t>Ransomware executes undetected on unmanaged or legacy-AV hosts</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Protect</t>
+          <t>Detect</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>PR.PS</t>
+          <t>DE.CM</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>PR.PS-01</t>
+          <t>DE.CM-09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Legacy / OT</t>
+          <t>Endpoints / servers</t>
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>Not tracked</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>Isolate legacy systems; virtual patching; compensating controls</t>
+        <v>4</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>IT / Operations</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>90-240 days</t>
+        <v>3.8</v>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="P17" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q17" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="S17" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="n">
-        <v>20</v>
+        <v>31</v>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>C12</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>Security Team</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>30-90 days</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>Deploy EDR with ransomware behaviour rules and auto-isolation</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>R04</t>
+          <t>R13</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Incomplete asset inventory / shadow IT</t>
+          <t>No tested incident response plan</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Unknown systems stay unpatched and unmonitored, becoming entry points</t>
+          <t>Slow, uncoordinated response increases dwell time and damage</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Identify</t>
+          <t>Respond</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>ID.AM</t>
+          <t>RS.MA</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>ID.AM-01</t>
+          <t>RS.MA-01</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>All IT assets</t>
+          <t>IR capability</t>
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>Manual spreadsheet inventory</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>Automated discovery; CMDB; owner assigned to each asset</t>
+        <v>5</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>IT Operations</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>30-120 days</t>
+        <v>4</v>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="O18" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="P18" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q18" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="S18" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="n">
-        <v>25</v>
+        <v>36</v>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>C16</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>CISO</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>30-90 days</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>Ransomware playbook; biannual tabletop exercises; IR retainer</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>R05</t>
+          <t>R19</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Weak vulnerability management</t>
+          <t>Outdated disaster recovery plan</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Scans run irregularly; findings not prioritised by exploitability</t>
+          <t>Recovery of critical systems takes weeks</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Identify</t>
+          <t>Recover</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>ID.RA</t>
+          <t>RC.RP</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>ID.RA-01</t>
+          <t>RC.RP-01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Servers / endpoints</t>
+          <t>DR plan</t>
         </is>
       </c>
       <c r="H19" s="2" t="n">
         <v>3</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>Quarterly scans</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>Continuous scanning; risk-based prioritisation; remediation tracking KPIs</t>
+        <v>5</v>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>Security Team</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>30-90 days</t>
+        <v>4</v>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="O19" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="P19" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q19" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="S19" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="n">
-        <v>50</v>
+        <v>36</v>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>C11, C21, C22</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>IT Operations</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>60-150 days</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>Update DR plan; restoration runbooks; clean-room recovery environment</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>R14</t>
+          <t>R04</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Poor crisis communication and legal notification</t>
+          <t>Incomplete asset inventory / shadow IT</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Delayed regulator/customer/staff notification causes fines and reputational loss</t>
+          <t>Unknown systems stay unpatched and unmonitored, becoming entry points</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Respond</t>
+          <t>Identify</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>RS.CO</t>
+          <t>ID.AM</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>RS.CO-02</t>
+          <t>ID.AM-01</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Legal / Comms</t>
+          <t>All IT assets</t>
         </is>
       </c>
       <c r="H20" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="I20" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>No defined process</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>Comms plan; legal counsel on call; regulatory notification matrix</t>
+      <c r="J20" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>Legal / Comms</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>30-90 days</t>
+      <c r="N20" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="O20" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="P20" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q20" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="S20" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="n">
-        <v>50</v>
+        <v>25</v>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>C06, C07</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>IT Operations</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>30-120 days</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>Automated discovery; CMDB; owner assigned to each asset</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>R16</t>
+          <t>R20</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>No board-level cyber governance</t>
+          <t>No post-incident improvement process</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Weak oversight leads to underfunded controls and unclear risk appetite</t>
+          <t>Same weaknesses repeat across incidents</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Govern</t>
+          <t>Identify</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>GV.OV</t>
+          <t>ID.IM</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>GV.OV-01</t>
+          <t>ID.IM-03</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Security programme</t>
         </is>
       </c>
       <c r="H21" s="2" t="n">
         <v>3</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>Annual CISO update</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>Quarterly board reporting; documented cyber risk appetite; KPIs/KRIs</t>
+        <v>3</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>Board / CISO</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>60-120 days</t>
+      <c r="N21" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="O21" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="P21" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q21" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="S21" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>C23</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>CISO</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>90-180 days</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory lessons-learned reviews; track corrective actions</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>R20</t>
+          <t>R16</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>No post-incident improvement process</t>
+          <t>No board-level cyber governance</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Same weaknesses repeat across incidents</t>
+          <t>Weak oversight leads to underfunded controls and unclear risk appetite</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Identify</t>
+          <t>Govern</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>ID.IM</t>
+          <t>GV.OV</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>ID.IM-03</t>
+          <t>GV.OV-01</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Security programme</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
         <v>3</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>Informal reviews</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>Mandatory lessons-learned reviews; track corrective actions</t>
+        <v>4</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>CISO</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>90-180 days</t>
+        <v>3.6</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="O22" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="P22" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q22" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="S22" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="n">
-        <v>56</v>
+        <v>28</v>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>C19</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>Board / CISO</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>60-120 days</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>Quarterly board reporting; documented cyber risk appetite; KPIs/KRIs</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -2478,50 +2469,50 @@
       <c r="I23" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>Documented decision framework; sanctions screening; cyber insurance review</t>
+      <c r="J23" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
         <v>2</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="O23" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>C20</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
         <is>
           <t>Legal / CFO</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
+      <c r="S23" s="2" t="inlineStr">
         <is>
           <t>60-120 days</t>
         </is>
       </c>
-      <c r="P23" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q23" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="S23" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="n">
-        <v>25</v>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>Documented decision framework; sanctions screening; cyber insurance review</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2535,171 +2526,908 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr"/>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Inherent Score</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Residual Score</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>control_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>csf_function</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>current_answer</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>risk_points_removed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>risks_affected</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>mean</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>C03</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Is multi-factor authentication (MFA) enforced on all VPN and remote access?</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Protect</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>R02, R21</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CSF Function</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Do you keep immutable or offline backups with separate credentials?</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Protect</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>R08</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Are logs centralised in a SIEM and monitored 24/7 (in-house or managed service)?</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Detect</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>R11, R12, R06</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>C08</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Do you use privileged access management and separate admin accounts (tiered admin)?</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Protect</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>R06, R07</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Do you test restoring from backups at least quarterly?</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Recover</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>R09, R19</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>C21</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Have you completed a business impact analysis with recovery targets (RTO/RPO)?</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Identify</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>R18, R19</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>C07</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Do you scan for vulnerabilities continuously and prioritise by exploitability?</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Identify</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>R05, R03, R04</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Do you use data-loss-prevention and egress filtering to spot bulk data leaving?</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Protect</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>C25</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Are legacy or unpatchable and OT systems isolated with compensating controls?</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Protect</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>R22</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>C05</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Are critical and actively exploited vulnerabilities patched within 72 hours?</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Protect</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>R03, R05</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>C18</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Do you assess vendor security and include security clauses in contracts?</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Govern</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>R15</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>C12</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Is EDR (endpoint detection and response) deployed on all endpoints and servers?</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Detect</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>R10, R07, R01</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>C24</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Do you use a password manager and monitor for leaked employee credentials?</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Protect</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>R21</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>C17</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Do you have a crisis communications and legal/regulatory notification plan?</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Respond</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>R14</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>C23</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Do you run lessons-learned reviews after every incident or exercise?</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Identify</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>R20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>C09</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Is the network segmented so workstations cannot freely reach servers and backups?</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Protect</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>R07</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>C22</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Is your disaster recovery plan updated and exercised in the last 12 months?</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Recover</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>R19, R09</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>C20</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Do you have a documented ransom-payment decision policy and cyber insurance?</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Govern</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>R17</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>C16</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Do you have a ransomware incident response playbook tested in the last 12 months?</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Respond</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>R13</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>C06</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Do you keep an automatically updated inventory of all IT assets?</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Identify</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>R04, R05</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>C19</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Does the board or executive team receive cyber risk reporting at least quarterly?</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Govern</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>R16</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>C15</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Is sensitive data classified and encrypted at rest?</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Protect</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>C04</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Is Remote Desktop (RDP) blocked from direct internet exposure?</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Protect</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>R02</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Do you run phishing awareness training and simulated phishing at least quarterly?</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Protect</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>R01, R21</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>csf_function</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>inherent_score</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>residual_score</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>risks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Govern</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Identify</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Protect</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Detect</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="D5" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C4" t="n">
-        <v>16</v>
-      </c>
-      <c r="D4" t="n">
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Respond</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D6" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E4" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Govern</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="D5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" t="n">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Identify</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C6" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="D6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" t="n">
-        <v>7</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Protect</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>9</v>
-      </c>
-      <c r="C7" t="n">
-        <v>19</v>
-      </c>
-      <c r="D7" t="n">
-        <v>9</v>
-      </c>
-      <c r="E7" t="n">
-        <v>8.9</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Recover</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B7" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="D7" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Respond</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" t="n">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>